--- a/data/trans_dic/P1427-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1427-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,09</t>
+          <t>1,7; 5,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,74</t>
+          <t>0,31; 2,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,56</t>
+          <t>1,85; 6,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 6,49</t>
+          <t>1,51; 6,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,02</t>
+          <t>0,46; 2,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,55</t>
+          <t>2,28; 5,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,89</t>
+          <t>1,06; 3,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,13</t>
+          <t>0,39; 1,55</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,15%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 2,4</t>
+          <t>0,39; 2,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>0,0; 1,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 3,64</t>
+          <t>1,24; 3,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,71</t>
+          <t>1,48; 4,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,51</t>
+          <t>0,45; 2,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,53</t>
+          <t>2,84; 5,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,97</t>
+          <t>1,13; 2,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,43</t>
+          <t>0,31; 1,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,11</t>
+          <t>2,32; 4,25</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,37</t>
+          <t>0,6; 3,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,42</t>
+          <t>0,55; 3,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,07</t>
+          <t>4,22; 8,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,75</t>
+          <t>0,87; 3,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,57</t>
+          <t>0,56; 3,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 7,79</t>
+          <t>4,07; 7,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,94</t>
+          <t>0,92; 2,92</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,85</t>
+          <t>0,83; 2,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,41</t>
+          <t>4,68; 7,33</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 4,23</t>
+          <t>1,11; 4,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,07</t>
+          <t>0,22; 2,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 3,94</t>
+          <t>0,97; 3,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,5</t>
+          <t>1,83; 5,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,5</t>
+          <t>0,57; 3,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,93</t>
+          <t>1,34; 3,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,16</t>
+          <t>1,84; 4,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,33</t>
+          <t>0,62; 2,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,88</t>
+          <t>1,38; 2,94</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,08; 8,46</t>
+          <t>2,41; 8,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1128,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 7,52</t>
+          <t>2,46; 6,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 9,46</t>
+          <t>2,64; 9,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 6,56</t>
+          <t>1,09; 6,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,38; 5,56</t>
+          <t>2,17; 5,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 7,74</t>
+          <t>3,15; 7,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,12</t>
+          <t>0,54; 3,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,63</t>
+          <t>2,77; 5,3</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,82</t>
+          <t>0,61; 3,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8,34; 14,02</t>
+          <t>8,31; 13,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,58</t>
+          <t>0,35; 3,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,61</t>
+          <t>1,35; 5,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,68; 14,66</t>
+          <t>9,72; 14,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,2</t>
+          <t>0,38; 2,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,05</t>
+          <t>1,3; 4,2</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,41</t>
+          <t>9,45; 13,18</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,89</t>
+          <t>1,09; 3,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,99</t>
+          <t>0,95; 2,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,96</t>
+          <t>2,11; 4,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,76</t>
+          <t>1,21; 3,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,65; 4,36</t>
+          <t>1,63; 4,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,19</t>
+          <t>5,22; 8,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,17</t>
+          <t>1,41; 3,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,2</t>
+          <t>1,6; 3,3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,47</t>
+          <t>3,94; 5,93</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,17</t>
+          <t>0,85; 3,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,92</t>
+          <t>0,42; 2,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,83</t>
+          <t>0,77; 2,17</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,56</t>
+          <t>1,31; 3,5</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,89</t>
+          <t>1,42; 3,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,94</t>
+          <t>1,74; 3,48</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,97</t>
+          <t>1,35; 2,98</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,46</t>
+          <t>1,12; 2,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,24</t>
+          <t>1,44; 2,55</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,56; 2,51</t>
+          <t>1,54; 2,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 1,42</t>
+          <t>0,75; 1,41</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,64</t>
+          <t>2,61; 3,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,28</t>
+          <t>2,14; 3,31</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 2,81</t>
+          <t>1,78; 2,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,97</t>
+          <t>3,93; 4,99</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,95; 2,7</t>
+          <t>1,95; 2,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,01</t>
+          <t>1,39; 2,03</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>3,18; 4,14</t>
+          <t>3,46; 4,19</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>4849</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5072; 17949</t>
+          <t>4996; 17567</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>922; 8042</t>
+          <t>919; 8151</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4005</t>
+          <t>0; 4802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5515; 18852</t>
+          <t>5328; 18971</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4451; 18730</t>
+          <t>4349; 18136</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1109; 5859</t>
+          <t>1452; 6640</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13421; 32329</t>
+          <t>13294; 31730</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6806; 22629</t>
+          <t>6176; 21384</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1522; 6807</t>
+          <t>2451; 9828</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11184</t>
+          <t>11635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20445</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31629</t>
+          <t>33798</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2004; 12109</t>
+          <t>1984; 11415</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5907</t>
+          <t>0; 5368</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5794; 18752</t>
+          <t>6558; 20334</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7441; 24679</t>
+          <t>7775; 25139</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2264; 13121</t>
+          <t>2330; 12744</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14008; 28444</t>
+          <t>15485; 30563</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11513; 30564</t>
+          <t>11618; 30191</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2799; 14706</t>
+          <t>3168; 14885</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22811; 42275</t>
+          <t>24854; 45651</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>19083</t>
+          <t>18732</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20505</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>39588</t>
+          <t>39374</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1940; 10931</t>
+          <t>1950; 11041</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1894; 10880</t>
+          <t>1752; 11032</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12893; 25515</t>
+          <t>13322; 27127</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2148; 12795</t>
+          <t>2981; 12937</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2047; 12008</t>
+          <t>1868; 11547</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14629; 27208</t>
+          <t>14502; 27704</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6097; 19530</t>
+          <t>6097; 19416</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5757; 18684</t>
+          <t>5428; 17680</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31539; 49260</t>
+          <t>31442; 49263</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6683</t>
+          <t>6961</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8794</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>16213</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4002; 15808</t>
+          <t>4167; 15871</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>828; 7664</t>
+          <t>831; 7815</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3571; 12305</t>
+          <t>3631; 12825</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7126; 21385</t>
+          <t>7106; 22261</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2234; 13574</t>
+          <t>2221; 13051</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4550; 13929</t>
+          <t>5643; 13435</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13237; 31725</t>
+          <t>14002; 32713</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4683; 17681</t>
+          <t>4706; 17796</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9875; 22693</t>
+          <t>10945; 23380</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8278</t>
+          <t>8691</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>16031</t>
+          <t>16728</t>
         </is>
       </c>
     </row>
@@ -2513,7 +2513,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4416; 17980</t>
+          <t>5134; 17769</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -2523,37 +2523,37 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5191; 13449</t>
+          <t>5058; 13340</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6120; 20783</t>
+          <t>5788; 20281</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2435; 14336</t>
+          <t>2377; 13676</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4953; 11570</t>
+          <t>4915; 11774</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14425; 33444</t>
+          <t>13619; 31689</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2346; 13390</t>
+          <t>2337; 13705</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11468; 21795</t>
+          <t>11971; 22907</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>28917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31020</t>
+          <t>31491</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>60103</t>
+          <t>60408</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 7096</t>
+          <t>0; 7552</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1586; 10062</t>
+          <t>1593; 9048</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22500; 37806</t>
+          <t>22508; 37161</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1016; 9946</t>
+          <t>986; 9018</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3561; 15326</t>
+          <t>3699; 15177</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24778; 37525</t>
+          <t>25521; 39055</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2129; 12122</t>
+          <t>2085; 12324</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>6926; 21737</t>
+          <t>6961; 22537</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51034; 70492</t>
+          <t>50399; 70302</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>22657</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42276</t>
+          <t>49548</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>62855</t>
+          <t>72205</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>8025; 25762</t>
+          <t>7205; 25121</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5601; 19602</t>
+          <t>6255; 19230</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13276; 30890</t>
+          <t>15117; 34587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>8563; 26064</t>
+          <t>8417; 26071</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>11378; 30163</t>
+          <t>11241; 30648</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20222; 61039</t>
+          <t>40295; 64348</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19446; 43035</t>
+          <t>19063; 41689</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>20654; 43113</t>
+          <t>21518; 44513</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40571; 80523</t>
+          <t>58681; 88295</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9631</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>32881</t>
+          <t>31470</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6446; 24732</t>
+          <t>6654; 23779</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3451; 14937</t>
+          <t>3272; 15645</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3492; 17015</t>
+          <t>6119; 17312</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>10881; 29297</t>
+          <t>10801; 28823</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11524; 32125</t>
+          <t>11716; 30476</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>15450; 42486</t>
+          <t>14474; 28940</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21363; 47610</t>
+          <t>21686; 47774</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17646; 39547</t>
+          <t>17920; 39503</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>20745; 53219</t>
+          <t>23529; 41576</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>105444</t>
+          <t>109619</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>156792</t>
+          <t>165427</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>262236</t>
+          <t>275046</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>53484; 86156</t>
+          <t>52928; 88371</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>25073; 48345</t>
+          <t>25492; 48016</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>80934; 125683</t>
+          <t>92165; 128153</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>75593; 116739</t>
+          <t>76098; 117673</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>63420; 99565</t>
+          <t>63030; 100160</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>124658; 181666</t>
+          <t>146671; 186357</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>136186; 188561</t>
+          <t>136074; 187911</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>93876; 139477</t>
+          <t>96676; 141206</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>226231; 294663</t>
+          <t>250908; 304092</t>
         </is>
       </c>
     </row>
